--- a/fung_presenceabsence.xlsx
+++ b/fung_presenceabsence.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oia08\Documents\GitHub\Kjuka_MasterThesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16E00EDB-5241-4E26-9D01-C98D6E116E83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47835284-06C4-49E2-8571-229D5E665F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{938CFD62-22EA-4B5C-9722-C0C614AE14DC}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="fung_presenceabsence" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="79">
   <si>
     <t>Treatment</t>
   </si>
@@ -137,9 +137,6 @@
     <t>C-Ex-5</t>
   </si>
   <si>
-    <t>MP</t>
-  </si>
-  <si>
     <t>MP-Sb-1</t>
   </si>
   <si>
@@ -263,17 +260,26 @@
     <t>Week_11</t>
   </si>
   <si>
-    <t>C</t>
-  </si>
-  <si>
     <t>Beetle</t>
+  </si>
+  <si>
+    <t>Week_2</t>
+  </si>
+  <si>
+    <t>Microplastic</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>No Beetle</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -291,6 +297,12 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -668,57 +680,57 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
@@ -765,10 +777,10 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2</v>
@@ -815,10 +827,10 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>2</v>
@@ -865,10 +877,10 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>2</v>
@@ -915,10 +927,10 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>2</v>
@@ -965,10 +977,10 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>2</v>
@@ -1015,10 +1027,10 @@
     </row>
     <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>2</v>
@@ -1065,10 +1077,10 @@
     </row>
     <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>2</v>
@@ -1115,10 +1127,10 @@
     </row>
     <row r="10" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>2</v>
@@ -1165,10 +1177,10 @@
     </row>
     <row r="11" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>12</v>
@@ -1215,10 +1227,10 @@
     </row>
     <row r="12" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B12" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>2</v>
@@ -1265,10 +1277,10 @@
     </row>
     <row r="13" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>12</v>
@@ -1315,10 +1327,10 @@
     </row>
     <row r="14" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>12</v>
@@ -1365,10 +1377,10 @@
     </row>
     <row r="15" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B15" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>2</v>
@@ -1415,10 +1427,10 @@
     </row>
     <row r="16" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B16" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>2</v>
@@ -1465,10 +1477,10 @@
     </row>
     <row r="17" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>2</v>
@@ -1515,10 +1527,10 @@
     </row>
     <row r="18" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B18" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>2</v>
@@ -1565,10 +1577,10 @@
     </row>
     <row r="19" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B19" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>2</v>
@@ -1615,10 +1627,10 @@
     </row>
     <row r="20" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B20" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>2</v>
@@ -1665,10 +1677,10 @@
     </row>
     <row r="21" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>12</v>
@@ -1715,10 +1727,10 @@
     </row>
     <row r="22" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B22" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>2</v>
@@ -1765,10 +1777,10 @@
     </row>
     <row r="23" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B23" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>12</v>
@@ -1815,10 +1827,10 @@
     </row>
     <row r="24" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>12</v>
@@ -1865,10 +1877,10 @@
     </row>
     <row r="25" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>2</v>
@@ -1915,10 +1927,10 @@
     </row>
     <row r="26" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B26" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>2</v>
@@ -1965,10 +1977,10 @@
     </row>
     <row r="27" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B27" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>2</v>
@@ -2015,10 +2027,10 @@
     </row>
     <row r="28" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B28" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>2</v>
@@ -2065,10 +2077,10 @@
     </row>
     <row r="29" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B29" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>2</v>
@@ -2115,10 +2127,10 @@
     </row>
     <row r="30" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B30" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>2</v>
@@ -2165,19 +2177,19 @@
     </row>
     <row r="31" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="B31" t="s">
-        <v>2</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="F31" s="1">
         <v>1</v>
@@ -2215,10 +2227,10 @@
     </row>
     <row r="32" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B32" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>2</v>
@@ -2227,7 +2239,7 @@
         <v>2</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -2265,10 +2277,10 @@
     </row>
     <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B33" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>2</v>
@@ -2277,7 +2289,7 @@
         <v>2</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -2315,10 +2327,10 @@
     </row>
     <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B34" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>2</v>
@@ -2327,7 +2339,7 @@
         <v>2</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -2365,10 +2377,10 @@
     </row>
     <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B35" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>2</v>
@@ -2377,7 +2389,7 @@
         <v>2</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -2415,10 +2427,10 @@
     </row>
     <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B36" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>2</v>
@@ -2427,7 +2439,7 @@
         <v>2</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -2465,10 +2477,10 @@
     </row>
     <row r="37" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B37" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>2</v>
@@ -2477,7 +2489,7 @@
         <v>2</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -2515,10 +2527,10 @@
     </row>
     <row r="38" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B38" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>2</v>
@@ -2527,7 +2539,7 @@
         <v>2</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
@@ -2565,10 +2577,10 @@
     </row>
     <row r="39" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B39" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>2</v>
@@ -2577,7 +2589,7 @@
         <v>2</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
@@ -2615,10 +2627,10 @@
     </row>
     <row r="40" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>2</v>
@@ -2627,7 +2639,7 @@
         <v>12</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -2665,10 +2677,10 @@
     </row>
     <row r="41" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B41" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>2</v>
@@ -2677,7 +2689,7 @@
         <v>2</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F41" s="1">
         <v>1</v>
@@ -2715,10 +2727,10 @@
     </row>
     <row r="42" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B42" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>2</v>
@@ -2727,7 +2739,7 @@
         <v>12</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F42" s="1">
         <v>1</v>
@@ -2765,10 +2777,10 @@
     </row>
     <row r="43" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B43" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>2</v>
@@ -2777,7 +2789,7 @@
         <v>12</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
@@ -2815,10 +2827,10 @@
     </row>
     <row r="44" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B44" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>2</v>
@@ -2827,7 +2839,7 @@
         <v>2</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
@@ -2865,10 +2877,10 @@
     </row>
     <row r="45" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B45" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>2</v>
@@ -2877,7 +2889,7 @@
         <v>2</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F45" s="1">
         <v>5</v>
@@ -2915,10 +2927,10 @@
     </row>
     <row r="46" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B46" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>2</v>
@@ -2927,7 +2939,7 @@
         <v>12</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F46" s="1">
         <v>1</v>
@@ -2965,10 +2977,10 @@
     </row>
     <row r="47" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B47" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>2</v>
@@ -2977,7 +2989,7 @@
         <v>12</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F47" s="1">
         <v>1</v>
@@ -3015,10 +3027,10 @@
     </row>
     <row r="48" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B48" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>2</v>
@@ -3027,7 +3039,7 @@
         <v>2</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -3065,10 +3077,10 @@
     </row>
     <row r="49" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B49" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>2</v>
@@ -3077,7 +3089,7 @@
         <v>2</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -3115,10 +3127,10 @@
     </row>
     <row r="50" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B50" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>2</v>
@@ -3127,7 +3139,7 @@
         <v>2</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -3165,10 +3177,10 @@
     </row>
     <row r="51" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B51" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>2</v>
@@ -3177,7 +3189,7 @@
         <v>12</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -3215,10 +3227,10 @@
     </row>
     <row r="52" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B52" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>2</v>
@@ -3227,7 +3239,7 @@
         <v>12</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F52" s="1">
         <v>1</v>
@@ -3265,10 +3277,10 @@
     </row>
     <row r="53" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B53" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>2</v>
@@ -3277,7 +3289,7 @@
         <v>2</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F53" s="1">
         <v>1</v>
@@ -3315,10 +3327,10 @@
     </row>
     <row r="54" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B54" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>2</v>
@@ -3327,7 +3339,7 @@
         <v>12</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F54" s="1">
         <v>1</v>
@@ -3365,10 +3377,10 @@
     </row>
     <row r="55" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B55" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>2</v>
@@ -3377,7 +3389,7 @@
         <v>2</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
@@ -3415,10 +3427,10 @@
     </row>
     <row r="56" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B56" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>2</v>
@@ -3427,7 +3439,7 @@
         <v>2</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F56" s="1">
         <v>1</v>
@@ -3465,10 +3477,10 @@
     </row>
     <row r="57" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B57" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>2</v>
@@ -3477,7 +3489,7 @@
         <v>2</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
@@ -3515,10 +3527,10 @@
     </row>
     <row r="58" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B58" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>2</v>
@@ -3527,7 +3539,7 @@
         <v>2</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F58" s="1">
         <v>0</v>
@@ -3565,10 +3577,10 @@
     </row>
     <row r="59" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B59" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>2</v>
@@ -3577,7 +3589,7 @@
         <v>2</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F59" s="1">
         <v>1</v>
@@ -3614,6 +3626,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/fung_presenceabsence.xlsx
+++ b/fung_presenceabsence.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oia08\Documents\GitHub\Kjuka_MasterThesis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Kjuka_MasterThesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47835284-06C4-49E2-8571-229D5E665F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA425F0A-5716-4B3C-8311-F29CC775F794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{938CFD62-22EA-4B5C-9722-C0C614AE14DC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{938CFD62-22EA-4B5C-9722-C0C614AE14DC}"/>
   </bookViews>
   <sheets>
     <sheet name="fung_presenceabsence" sheetId="1" r:id="rId1"/>
@@ -266,13 +266,13 @@
     <t>Week_2</t>
   </si>
   <si>
-    <t>Microplastic</t>
-  </si>
-  <si>
-    <t>Control</t>
-  </si>
-  <si>
     <t>No Beetle</t>
+  </si>
+  <si>
+    <t>Control,</t>
+  </si>
+  <si>
+    <t>Microplastic,</t>
   </si>
 </sst>
 </file>
@@ -670,12 +670,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65965339-2180-4FDD-A798-F46825C0ED1B}">
   <dimension ref="A1:P59"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="15.85546875" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -725,12 +725,12 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
@@ -775,12 +775,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2</v>
@@ -825,12 +825,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>2</v>
@@ -875,12 +875,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>2</v>
@@ -925,12 +925,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>2</v>
@@ -975,12 +975,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>2</v>
@@ -1025,12 +1025,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>2</v>
@@ -1075,12 +1075,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>2</v>
@@ -1125,12 +1125,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>2</v>
@@ -1175,7 +1175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>77</v>
       </c>
@@ -1225,12 +1225,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>2</v>
@@ -1275,7 +1275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>77</v>
       </c>
@@ -1325,7 +1325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>77</v>
       </c>
@@ -1375,12 +1375,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>2</v>
@@ -1425,12 +1425,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>2</v>
@@ -1475,7 +1475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>77</v>
       </c>
@@ -1525,12 +1525,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>2</v>
@@ -1575,12 +1575,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>2</v>
@@ -1625,12 +1625,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>2</v>
@@ -1675,7 +1675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>77</v>
       </c>
@@ -1725,12 +1725,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>2</v>
@@ -1775,7 +1775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>77</v>
       </c>
@@ -1825,7 +1825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>77</v>
       </c>
@@ -1875,7 +1875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>77</v>
       </c>
@@ -1925,12 +1925,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B26" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>2</v>
@@ -1975,12 +1975,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B27" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>2</v>
@@ -2025,12 +2025,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B28" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>2</v>
@@ -2075,12 +2075,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>2</v>
@@ -2125,12 +2125,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>2</v>
@@ -2175,12 +2175,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>2</v>
@@ -2225,12 +2225,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B32" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>2</v>
@@ -2275,12 +2275,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B33" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>2</v>
@@ -2325,12 +2325,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B34" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>2</v>
@@ -2375,12 +2375,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B35" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>2</v>
@@ -2425,12 +2425,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B36" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>2</v>
@@ -2475,12 +2475,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B37" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>2</v>
@@ -2525,12 +2525,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B38" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>2</v>
@@ -2575,12 +2575,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B39" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>2</v>
@@ -2625,9 +2625,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B40" t="s">
         <v>74</v>
@@ -2675,12 +2675,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B41" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>2</v>
@@ -2725,9 +2725,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B42" t="s">
         <v>74</v>
@@ -2775,9 +2775,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B43" t="s">
         <v>74</v>
@@ -2825,9 +2825,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B44" t="s">
         <v>74</v>
@@ -2875,12 +2875,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B45" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>2</v>
@@ -2925,12 +2925,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B46" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>2</v>
@@ -2975,9 +2975,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B47" t="s">
         <v>74</v>
@@ -3025,12 +3025,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B48" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>2</v>
@@ -3075,12 +3075,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B49" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>2</v>
@@ -3125,12 +3125,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B50" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>2</v>
@@ -3175,9 +3175,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B51" t="s">
         <v>74</v>
@@ -3225,9 +3225,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B52" t="s">
         <v>74</v>
@@ -3275,12 +3275,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B53" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>2</v>
@@ -3325,9 +3325,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B54" t="s">
         <v>74</v>
@@ -3375,12 +3375,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B55" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>2</v>
@@ -3425,12 +3425,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B56" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>2</v>
@@ -3475,12 +3475,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B57" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>2</v>
@@ -3525,12 +3525,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B58" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>2</v>
@@ -3575,12 +3575,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B59" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>2</v>
